--- a/data/trans_orig/IP31KM16_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM16_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>13949</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8487</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21268</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,51%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>7,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8878</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4597</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14635</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>14,39%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>5220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23344</t>
+          <t>16069</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24149</t>
+          <t>23334</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16746</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33887</t>
+          <t>33060</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>107260</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>99941</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>112722</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,49%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>92831</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>87074</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>97112</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,27%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>85,61%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119906</t>
+          <t>90964</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111832</t>
+          <t>84280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125846</t>
+          <t>95129</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>212737</t>
+          <t>198224</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>202999</t>
+          <t>188498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>220140</t>
+          <t>205016</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13617</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8373</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20580</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12879</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7516</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>19272</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>20,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14543</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>19536</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>27422</t>
+          <t>27041</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37549</t>
+          <t>36847</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>76263</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69300</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>81507</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77,1%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>80513</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>74120</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>85876</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>79165</t>
+          <t>81985</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70967</t>
+          <t>75874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84057</t>
+          <t>87211</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>85,93%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>159679</t>
+          <t>158249</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>149552</t>
+          <t>148443</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>166622</t>
+          <t>165153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>89880</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>93392</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>95410</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>187101</t>
+          <t>185290</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4559</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9050</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7904</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4176</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12626</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,21%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>8308</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12558</t>
+          <t>12867</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7847</t>
+          <t>8288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18951</t>
+          <t>19703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>51285</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46794</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>53939</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,84%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>42185</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>37463</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>45913</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>84,22%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>57680</t>
+          <t>43702</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52307</t>
+          <t>38307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60529</t>
+          <t>47268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>99864</t>
+          <t>94987</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>93471</t>
+          <t>88151</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>104575</t>
+          <t>99566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,32%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>50089</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>52010</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112422</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>23694</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16262</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32919</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>12,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,24%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>32994</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>20988</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50970</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>15,31%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23976</t>
+          <t>25510</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16557</t>
+          <t>18073</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>35826</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>49204</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43235</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77966</t>
+          <t>62536</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>173619</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>164394</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>181051</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>87,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,76%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>182543</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>164567</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>194549</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>90,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>188682</t>
+          <t>151130</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>178606</t>
+          <t>140814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>196101</t>
+          <t>158567</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>371226</t>
+          <t>324749</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>350230</t>
+          <t>311417</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>384961</t>
+          <t>335441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>89,7%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22536</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>11443</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>47570</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>32,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>14139</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8995</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>20853</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25854</t>
+          <t>14791</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13196</t>
+          <t>9211</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57169</t>
+          <t>21621</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39994</t>
+          <t>37326</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26815</t>
+          <t>25498</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72553</t>
+          <t>62947</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>123050</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>98016</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>134143</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>67,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>92,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>101370</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>94656</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>106514</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>87,76%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>81,95%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>92,21%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>133607</t>
+          <t>100675</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102292</t>
+          <t>93845</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146265</t>
+          <t>106255</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>234976</t>
+          <t>223726</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>202417</t>
+          <t>198105</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>248155</t>
+          <t>235554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>145586</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>159461</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>274970</t>
+          <t>261052</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5585</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2228</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>10307</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>8,48%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>15,65%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>9423</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5549</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>14642</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>13,68%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>21,25%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>5605</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10756</t>
+          <t>14990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15029</t>
+          <t>14787</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22154</t>
+          <t>21675</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,91%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60278</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>55556</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>63635</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>91,52%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>84,35%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>96,62%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>59472</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>54253</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>63346</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>86,32%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>78,75%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>91,95%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>63426</t>
+          <t>61154</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58275</t>
+          <t>55366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66704</t>
+          <t>64948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>122896</t>
+          <t>121433</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>115771</t>
+          <t>114545</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128040</t>
+          <t>126382</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>137925</t>
+          <t>136220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>83940</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>66338</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>110565</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9,82%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>16,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>86218</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>69441</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>106607</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>16,52%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>89903</t>
+          <t>80621</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71721</t>
+          <t>66515</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126190</t>
+          <t>95544</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>176121</t>
+          <t>164561</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>150786</t>
+          <t>142538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>216428</t>
+          <t>195565</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>591755</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>565130</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>609357</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>87,58%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>83,64%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>787</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>558913</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>538524</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>575690</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>86,64%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>89,24%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>642465</t>
+          <t>529611</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>606178</t>
+          <t>514688</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>660647</t>
+          <t>543717</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>84,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1201378</t>
+          <t>1121366</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1161071</t>
+          <t>1090362</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1226713</t>
+          <t>1143389</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>675695</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>902</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>645131</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>923</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>732368</t>
+          <t>610232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1377499</t>
+          <t>1285927</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
